--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Traites_LRA_tele" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Plage_diametre" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Longueur_tete" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Diametre_FP2E" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A23"/>
+  <dimension ref="A1:A27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -494,76 +495,104 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  • Diametre_FP2E         : diamètre(s) correspondant à chaque lettre FP2E.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Règles :</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Mode = Radio, Tele ou Manuelle (selon l'onglet).</t>
+          <t>Règles :</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Une valeur vide dans 'Type Compteur' (onglet Longueur_tete) = s'applique</t>
+          <t xml:space="preserve">  - Mode = Radio, Tele ou Manuelle (selon l'onglet).</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">    à toutes les valeurs de la marque. Une ligne avec un Type précis est</t>
+          <t xml:space="preserve">  - Une valeur vide dans 'Type Compteur' (onglet Longueur_tete) = s'applique</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">    prioritaire sur la ligne générale.</t>
+          <t xml:space="preserve">    à toutes les valeurs de la marque. Une ligne avec un Type précis est</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Ne renommez PAS les onglets ni les colonnes (en-têtes).</t>
+          <t xml:space="preserve">    prioritaire sur la ligne générale.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - En cas d'erreur de saisie, l'application ignore la partie concernée et</t>
+          <t xml:space="preserve">  - Onglet Diametre_FP2E : une ligne par (Lettre, Diametre). Une lettre qui</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">    utilise les valeurs par défaut (elle ne plante pas).</t>
+          <t xml:space="preserve">    accepte plusieurs diamètres a plusieurs lignes (ex. G -&gt; 60 et G -&gt; 65).</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    Le 1er diamètre listé pour une lettre sert de correction proposée.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Astuce : pour repartir de zéro, supprimez ce fichier et relancez l'application :</t>
+          <t xml:space="preserve">  - Ne renommez PAS les onglets ni les colonnes (en-têtes).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - En cas d'erreur de saisie, l'application ignore la partie concernée et</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    utilise les valeurs par défaut (elle ne plante pas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Astuce : pour repartir de zéro, supprimez ce fichier et relancez l'application :</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
         <is>
           <t>il sera recréé avec les valeurs par défaut.</t>
         </is>
@@ -1347,4 +1376,214 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Lettre</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Diametre</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>U</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>H</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>J</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>L</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>400</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -1200,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>400</v>
+        <v>80</v>
       </c>
     </row>
   </sheetData>

--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -1214,7 +1214,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -1365,11 +1365,51 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
+          <t>SAPPEL (C)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>INT3</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Tele</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>SAPPEL (H)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>INT3</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Tele</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>ITRON</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="n">
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="n">
         <v>8</v>
       </c>
     </row>

--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Notice" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Marques_autorisees" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Type_Compteur_autorises" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Traites_LRA_tele" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="ProtocoleRadio_commune" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Plage_diametre" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Longueur_tete" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Diametre_FP2E" sheetId="7" state="visible" r:id="rId7"/>
@@ -23,13 +23,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -419,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="70" customWidth="1" min="1" max="1"/>
@@ -476,7 +488,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">  • Traites_LRA_tele      : préfixes de Traité en LRA (télé). Le reste = SGX.</t>
+          <t xml:space="preserve">  • ProtocoleRadio_commune : protocole Radio attendu par commune (télé).</t>
         </is>
       </c>
     </row>
@@ -563,36 +575,64 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - Ne renommez PAS les onglets ni les colonnes (en-têtes).</t>
+          <t xml:space="preserve">  - Onglet ProtocoleRadio_commune : une ligne par (Commune, Protocole Radio).</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">  - En cas d'erreur de saisie, l'application ignore la partie concernée et</t>
+          <t xml:space="preserve">    En télérelève, le protocole de chaque ligne doit correspondre à celui de</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">    utilise les valeurs par défaut (elle ne plante pas).</t>
+          <t xml:space="preserve">    sa commune. La comparaison ignore la casse et les accents. Une commune</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    absente de ce tableau est signalée (protocole non vérifié).</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Astuce : pour repartir de zéro, supprimez ce fichier et relancez l'application :</t>
+          <t xml:space="preserve">  - Ne renommez PAS les onglets ni les colonnes (en-têtes).</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  - En cas d'erreur de saisie, l'application ignore la partie concernée et</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    utilise les valeurs par défaut (elle ne plante pas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Astuce : pour repartir de zéro, supprimez ce fichier et relancez l'application :</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>il sera recréé avec les valeurs par défaut.</t>
         </is>
@@ -617,12 +657,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Marque</t>
         </is>
@@ -802,7 +842,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Type Compteur</t>
         </is>
@@ -1099,58 +1139,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:B1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Prefixe Traite</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>312</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>455</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>863</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>895</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>903</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>956</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Commune</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Protocole Radio</t>
         </is>
       </c>
     </row>
@@ -1174,17 +1178,17 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Marque</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Min</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Max</t>
         </is>
@@ -1224,22 +1228,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Mode</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Marque</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Type Compteur</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Longueur</t>
         </is>
@@ -1432,12 +1436,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Lettre</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Diametre</t>
         </is>

--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -651,8 +651,6 @@
           <t>SAPPEL (C)</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -660,8 +658,6 @@
           <t>SAPPEL (H)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -669,8 +665,6 @@
           <t>ITRON</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4311,7 +4305,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -4321,7 +4315,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
     </row>
     <row r="11">
@@ -4451,13 +4445,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>KAMSTRUP</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
         <v>8</v>
       </c>
@@ -4504,8 +4496,6 @@
           <t>KAMSTRUP</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr"/>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>WMS</t>

--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -677,7 +677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -825,6 +825,126 @@
       <c r="B12" t="inlineStr">
         <is>
           <t>U Kamstrup</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>U KAMSTRUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>INTEGRA</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>SAPPEL (C)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>SENSUS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SAPPEL (H)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>ITRON</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>KAIFA</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>KAMSTRUP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>KROHNE</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Manuelle</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>ZENNER</t>
         </is>
       </c>
     </row>

--- a/regles_anomalies.xlsx
+++ b/regles_anomalies.xlsx
@@ -15,7 +15,6 @@
     <sheet name="Diametre_FP2E" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Longueur_compteur" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Protocole_par_marque" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Compteurs_FP2E" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -619,58 +618,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Marque</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Année min</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Mode de relève</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SAPPEL (C)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>SAPPEL (H)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ITRON</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
